--- a/docs/harmonogram.xlsx
+++ b/docs/harmonogram.xlsx
@@ -1,23 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kubak\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9F593D-D3B1-46FC-A540-41BD1A9A352F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4507"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5541C825-59C0-4E5F-ACA2-E98AA58ECD95}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="125725"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="22">
   <si>
     <t>Dawid</t>
   </si>
@@ -90,13 +84,25 @@
   </si>
   <si>
     <t>Napisać i zaimplementować algorytm Boyera i Moora do kopmresji pliku z danymi jsona</t>
+  </si>
+  <si>
+    <t>Napisać i zaimplementować algorytm Boyera i Moora do kopmresji pliku z danymi jsona. Pzygotowanie dokumentacji.</t>
+  </si>
+  <si>
+    <t>Sprawdzenie programu pod kątem błędów</t>
+  </si>
+  <si>
+    <t>Przygoowanie testów</t>
+  </si>
+  <si>
+    <t>Praca nad generatorem - implementacja sieci przesyłowych?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -159,6 +165,9 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -220,7 +229,7 @@
     </a:clrScheme>
     <a:fontScheme name="Pakiet Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -272,7 +281,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -486,24 +495,24 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D9BB1C2-395D-48E4-9475-9BC7BBE93EDA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="29.21875" customWidth="1"/>
+    <col min="1" max="1" width="29.25" customWidth="1"/>
     <col min="2" max="3" width="27" customWidth="1"/>
-    <col min="4" max="4" width="26.88671875" customWidth="1"/>
-    <col min="5" max="5" width="11.21875" customWidth="1"/>
+    <col min="4" max="4" width="26.875" customWidth="1"/>
+    <col min="5" max="5" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -520,7 +529,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="44.45" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -537,7 +546,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="57">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -554,7 +563,7 @@
         <v>46120</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="42.75">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -571,7 +580,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -588,7 +597,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -605,7 +614,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -622,7 +631,7 @@
         <v>46148</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
@@ -639,7 +648,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="114">
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
@@ -656,25 +665,41 @@
         <v>46162</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E10" s="5">
         <v>46169</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+    <row r="11" spans="1:5" ht="57">
+      <c r="A11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="E11" s="5">
         <v>46176</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -683,7 +708,7 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>

--- a/docs/harmonogram.xlsx
+++ b/docs/harmonogram.xlsx
@@ -92,10 +92,10 @@
     <t>Sprawdzenie programu pod kątem błędów</t>
   </si>
   <si>
-    <t>Przygoowanie testów</t>
-  </si>
-  <si>
-    <t>Praca nad generatorem - implementacja sieci przesyłowych?</t>
+    <t>Implementacja ieci przesyłowej.</t>
+  </si>
+  <si>
+    <t>Pzygoowanie testów do algorytmów.</t>
   </si>
 </sst>
 </file>
@@ -495,7 +495,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -684,13 +684,13 @@
     </row>
     <row r="11" spans="1:5" ht="57">
       <c r="A11" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>18</v>

--- a/docs/harmonogram.xlsx
+++ b/docs/harmonogram.xlsx
@@ -89,13 +89,13 @@
     <t>Napisać i zaimplementować algorytm Boyera i Moora do kopmresji pliku z danymi jsona. Pzygotowanie dokumentacji.</t>
   </si>
   <si>
-    <t>Sprawdzenie programu pod kątem błędów</t>
-  </si>
-  <si>
     <t>Implementacja ieci przesyłowej.</t>
   </si>
   <si>
     <t>Pzygoowanie testów do algorytmów.</t>
+  </si>
+  <si>
+    <t>Sprawdzenie programu pod kątem błędów, naprawić odpalanie index.html (blokuje CORS)</t>
   </si>
 </sst>
 </file>
@@ -495,7 +495,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -684,13 +684,13 @@
     </row>
     <row r="11" spans="1:5" ht="57">
       <c r="A11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>18</v>
